--- a/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF546BD-2A19-4B7F-87DF-F630D49814BB}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3B9966-3308-4897-94B4-1FB6DA845AA6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -249,27 +249,15 @@
     <t>CHE114</t>
   </si>
   <si>
-    <t>Chemistry 114 (N)</t>
-  </si>
-  <si>
     <t>CHE116</t>
   </si>
   <si>
-    <t>Chemistry 116 (N)</t>
-  </si>
-  <si>
     <t>CHE124</t>
   </si>
   <si>
-    <t>Chemistry 124 (N)</t>
-  </si>
-  <si>
     <t>CHM126</t>
   </si>
   <si>
-    <t>Chemistry 126 (N)</t>
-  </si>
-  <si>
     <t>CHM211</t>
   </si>
   <si>
@@ -564,15 +552,9 @@
     <t>LFS151</t>
   </si>
   <si>
-    <t>Life Sciences 151 (SF)</t>
-  </si>
-  <si>
     <t>LFS152</t>
   </si>
   <si>
-    <t>Life Sciences 152 (SF)</t>
-  </si>
-  <si>
     <t>LSC141</t>
   </si>
   <si>
@@ -588,18 +570,12 @@
     <t>MAM115</t>
   </si>
   <si>
-    <t>Mathematics 115 (N)</t>
-  </si>
-  <si>
     <t>MAM150</t>
   </si>
   <si>
     <t>MAM151</t>
   </si>
   <si>
-    <t>Mathematics 151 (SF)</t>
-  </si>
-  <si>
     <t>MAT105</t>
   </si>
   <si>
@@ -951,15 +927,9 @@
     <t>PHY151</t>
   </si>
   <si>
-    <t>Physics 151 (SF)</t>
-  </si>
-  <si>
     <t>PHY152</t>
   </si>
   <si>
-    <t>Physics 152 (SF)</t>
-  </si>
-  <si>
     <t>PHY212</t>
   </si>
   <si>
@@ -1044,9 +1014,6 @@
     <t>Pharmacy Practice 324</t>
   </si>
   <si>
-    <t>PPR214, PPR224, PPR314 (min 40%)</t>
-  </si>
-  <si>
     <t>PPR404</t>
   </si>
   <si>
@@ -1089,9 +1056,6 @@
     <t>STA151</t>
   </si>
   <si>
-    <t>Statistics 151 (SF)</t>
-  </si>
-  <si>
     <t>STA211</t>
   </si>
   <si>
@@ -1104,9 +1068,6 @@
     <t>Statistics 221</t>
   </si>
   <si>
-    <t>STA211 (qualified for exam)</t>
-  </si>
-  <si>
     <t>STA331</t>
   </si>
   <si>
@@ -1137,45 +1098,9 @@
     <t>Year 1</t>
   </si>
   <si>
-    <t>LSC141, LSC142 (or LFS151, LFS152) AND CHE114 (or CHE124, CHE116, CHM126)</t>
-  </si>
-  <si>
-    <t>CHE114/124, LSC141/142 (or LFS/MBS equivalents)</t>
-  </si>
-  <si>
-    <t>CHE114, CHE124, LSC141, LSC142 (or equivalents)</t>
-  </si>
-  <si>
-    <t>CHE114/124, LSC141/142 (or equivalents)</t>
-  </si>
-  <si>
-    <t>Bachelor of Pharmacy (3305)</t>
-  </si>
-  <si>
-    <t>BSc Biotechnology (3211)</t>
-  </si>
-  <si>
-    <t>BSc Chemical Sciences (3220)</t>
-  </si>
-  <si>
-    <t>BSc Mathematics and Statistical Sciences (3227)</t>
-  </si>
-  <si>
-    <t>ECO151 (or ECO241)</t>
-  </si>
-  <si>
-    <t>ECO152 (or equivalent)</t>
-  </si>
-  <si>
     <t>ECO151, ECO152</t>
   </si>
   <si>
-    <t>BSc Environment and Water Science (3331)</t>
-  </si>
-  <si>
-    <t>BSc Computer Science (3221)</t>
-  </si>
-  <si>
     <t>IFS131/132, COS101/114, COS124, EED127, ISC153, MAT151/103, MAT104, STA111, IFS131/132, COS101, PHY151, MAT151</t>
   </si>
   <si>
@@ -1185,24 +1110,9 @@
     <t>Introduction to Science 153</t>
   </si>
   <si>
-    <t>BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
     <t>Introduction to Mathematics 150</t>
   </si>
   <si>
-    <t>BSc Applied Geology Extended (3011)</t>
-  </si>
-  <si>
-    <t>MAT105 (or equivalent)</t>
-  </si>
-  <si>
-    <t>APM112, MAT105 (or equivalent)</t>
-  </si>
-  <si>
-    <t>BSc Medical Bioscience (3230)</t>
-  </si>
-  <si>
     <t>MBS231, MBS232</t>
   </si>
   <si>
@@ -1215,18 +1125,6 @@
     <t>Year 4</t>
   </si>
   <si>
-    <t>CHE114, CHE124, PCH233/ (min 40% in PCH233)</t>
-  </si>
-  <si>
-    <t>PCH232, PCH233, PCH312/ (min 40% in PCH312)</t>
-  </si>
-  <si>
-    <t>HUB113, HUB123, PHC123, PHA116/ (min 40% for PHC213)</t>
-  </si>
-  <si>
-    <t>PHC213, PHC223, PHC313/ (min 40% for PHC313)</t>
-  </si>
-  <si>
     <t>MAT103 or MAT105</t>
   </si>
   <si>
@@ -1242,100 +1140,202 @@
     <t>PHY212/217, MAT105/103/152</t>
   </si>
   <si>
-    <t>PCE231, PHC213, PPR214/ (min 40% in each)</t>
-  </si>
-  <si>
-    <t>STA111/125/151 (or equivalent)</t>
-  </si>
-  <si>
-    <t>MAT105 (or equivalent) AND STA111/125/151</t>
-  </si>
-  <si>
-    <t>(General Science Elective)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Environment and Water Science (3331),BSc Applied Geology Extended (3011)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Applied Geology Extended (3011)</t>
-  </si>
-  <si>
-    <t>BSc Mathematics and Statistical Sciences (3227),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity and Conservation Biology (3217),BSc Environment and Water Science (3331),BSc Biodiversity and Conservation Biology Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity and Conservation Biology (3217),BSc Biodiversity and Conservation Biology Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Biotechnology (3211),BSc Chemical Sciences (3220),BSc Medical Bioscience (3230)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Chemical Sciences (3220),BSc Physical Science (3233),Bachelor of Pharmacy (3305),BSc Applied Geology Extended (3011),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Environment and Water Science (3331),BSc Medical Bioscience (3230),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Chemical Sciences (3220),BSc Physical Science (3233),BSc Applied Geology Extended (3011),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Chemical Sciences (3220),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Computer Science (3221),BSc Mathematics and Statistical Sciences (3227),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biotechnology (3211),BSc Computer Science (3221),BSc Mathematics and Statistical Sciences (3227),BSc Medical Bioscience (3230),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Environment and Water Science (3331),BSc Mathematics and Statistical Sciences (3227),BSc Medical Bioscience (3230),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Computer Science (3221),BSc Environment and Water Science (3331),BSc Mathematics and Statistical Sciences (3227),BSc Medical Bioscience (3230),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Environment and Water Science (3331),BSc Physical Science (3233),BSc Applied Geology Extended (3011),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biodiversity (3217),BSc Environment and Water Science (3331),BSc Applied Geology Extended (3011),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Environment and Water Science (3331),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology Extended (3011),BSc Biodiversity Extended (3015)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Chemical Sciences (3220),BSc Environment and Water Science (3331),BSc Medical Bioscience (3230)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Chemical Sciences (3220),BSc Environment and Water Science (3331)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biotechnology (3211),Bachelor of Pharmacy (3305)</t>
-  </si>
-  <si>
-    <t>BSc Chemical Sciences (3220),BSc Computer Science (3221),BSc Mathematics and Statistical Sciences (3227),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Applied Geology (3214),BSc Biotechnology (3211),BSc Environment and Water Science (3331),BSc Mathematics and Statistical Sciences (3227)</t>
-  </si>
-  <si>
-    <t>BSc Chemical Sciences (3220),BSc Computer Science (3221),BSc Environment and Water Science (3331),BSc Mathematics and Statistical Sciences (3227),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Computer Science (3221),BSc Physical Science (3233)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Computer Science (3221),BSc Environment and Water Science (3331),BSc Mathematics and Statistical Sciences (3227)</t>
-  </si>
-  <si>
-    <t>BSc Computer Science (3221),BSc Mathematics and Statistical Sciences (3227)</t>
-  </si>
-  <si>
-    <t>BSc Biodiversity (3217),BSc Biotechnology (3211),BSc Environment and Water Science (3331),BSc Medical Bioscience (3230)</t>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Applied Geology Extended  3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSC141, LSC142 (or LFS151, LFS152  AND CHE114 (or CHE124, CHE116, CHM126 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Medical Bioscience  3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHE114/124, LSC141/142 (or LFS/MBS equivalents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHE114, CHE124, LSC141, LSC142 (or equivalents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHE114/124, LSC141/142 (or equivalents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor of Pharmacy  3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology  3211 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry 114 (N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,Bachelor of Pharmacy  3305 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry 116 (N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry 124 (N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry 126 (N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences  3220 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECO151 (or ECO241 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECO152 (or equivalent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Environment and Water Science  3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science  3221 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Sciences 151 (SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity Extended  3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Sciences 152 (SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematics 115 (N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,Bachelor of Pharmacy  3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematics 151 (SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended  3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAT105 (or equivalent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM112, MAT105 (or equivalent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Medical Bioscience  3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHE114, CHE124, PCH233/ (min 40% in PCH233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCH232, PCH233, PCH312/ (min 40% in PCH312 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUB113, HUB123, PHC123, PHA116/ (min 40% for PHC213 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHC213, PHC223, PHC313/ (min 40% for PHC313 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physics 151 (SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physics 152 (SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Physical Science  3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCE231, PHC213, PPR214/ (min 40% in each </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPR214, PPR224, PPR314 (min 40% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STA111/125/151 (or equivalent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics 151 (SF </t>
+  </si>
+  <si>
+    <t>MAT105 (or equivalent  AND STA111/125/151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STA211 (qualified for exam </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> General Science Elective </t>
   </si>
 </sst>
 </file>
@@ -1406,6 +1406,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1706,10 +1710,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -1726,10 +1730,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1746,10 +1750,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
@@ -1766,10 +1770,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1786,10 +1790,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
@@ -1806,10 +1810,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -1826,10 +1830,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1846,10 +1850,10 @@
         <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>6</v>
@@ -1866,10 +1870,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>6</v>
@@ -1886,10 +1890,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -1906,10 +1910,10 @@
         <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
@@ -1926,10 +1930,10 @@
         <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
@@ -1946,13 +1950,13 @@
         <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -1966,10 +1970,10 @@
         <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>34</v>
@@ -1986,10 +1990,10 @@
         <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2006,10 +2010,10 @@
         <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -2026,10 +2030,10 @@
         <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>49</v>
@@ -2046,13 +2050,13 @@
         <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -2066,13 +2070,13 @@
         <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -2086,13 +2090,13 @@
         <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -2106,10 +2110,10 @@
         <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>6</v>
@@ -2126,13 +2130,13 @@
         <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -2146,13 +2150,13 @@
         <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -2166,13 +2170,13 @@
         <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -2186,10 +2190,10 @@
         <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>66</v>
@@ -2206,10 +2210,10 @@
         <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -2226,10 +2230,10 @@
         <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>66</v>
@@ -2246,10 +2250,10 @@
         <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>66</v>
@@ -2263,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>383</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>6</v>
@@ -2280,16 +2284,16 @@
     </row>
     <row r="31" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>385</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>6</v>
@@ -2300,16 +2304,16 @@
     </row>
     <row r="32" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>6</v>
@@ -2320,16 +2324,16 @@
     </row>
     <row r="33" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>6</v>
@@ -2340,19 +2344,19 @@
     </row>
     <row r="34" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -2360,19 +2364,19 @@
     </row>
     <row r="35" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -2380,19 +2384,19 @@
     </row>
     <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2400,19 +2404,19 @@
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2420,19 +2424,19 @@
     </row>
     <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2440,19 +2444,19 @@
     </row>
     <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2460,19 +2464,19 @@
     </row>
     <row r="40" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2480,16 +2484,16 @@
     </row>
     <row r="41" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>6</v>
@@ -2500,16 +2504,16 @@
     </row>
     <row r="42" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>6</v>
@@ -2520,16 +2524,16 @@
     </row>
     <row r="43" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>6</v>
@@ -2540,19 +2544,19 @@
     </row>
     <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2560,19 +2564,19 @@
     </row>
     <row r="45" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2580,19 +2584,19 @@
     </row>
     <row r="46" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2600,19 +2604,19 @@
     </row>
     <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2620,16 +2624,16 @@
     </row>
     <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>6</v>
@@ -2640,16 +2644,16 @@
     </row>
     <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>6</v>
@@ -2660,19 +2664,19 @@
     </row>
     <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2680,19 +2684,19 @@
     </row>
     <row r="51" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2700,19 +2704,19 @@
     </row>
     <row r="52" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2720,39 +2724,39 @@
     </row>
     <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2760,19 +2764,19 @@
     </row>
     <row r="55" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2780,19 +2784,19 @@
     </row>
     <row r="56" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2800,19 +2804,19 @@
     </row>
     <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2820,19 +2824,19 @@
     </row>
     <row r="58" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2840,19 +2844,19 @@
     </row>
     <row r="59" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2860,16 +2864,16 @@
     </row>
     <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>6</v>
@@ -2880,16 +2884,16 @@
     </row>
     <row r="61" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>6</v>
@@ -2900,16 +2904,16 @@
     </row>
     <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>6</v>
@@ -2920,16 +2924,16 @@
     </row>
     <row r="63" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>6</v>
@@ -2940,16 +2944,16 @@
     </row>
     <row r="64" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>9</v>
@@ -2960,16 +2964,16 @@
     </row>
     <row r="65" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>9</v>
@@ -2980,39 +2984,39 @@
     </row>
     <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -3020,19 +3024,19 @@
     </row>
     <row r="68" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -3040,19 +3044,19 @@
     </row>
     <row r="69" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -3060,19 +3064,19 @@
     </row>
     <row r="70" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -3080,16 +3084,16 @@
     </row>
     <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>6</v>
@@ -3100,16 +3104,16 @@
     </row>
     <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>6</v>
@@ -3120,16 +3124,16 @@
     </row>
     <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>6</v>
@@ -3140,19 +3144,19 @@
     </row>
     <row r="74" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -3160,19 +3164,19 @@
     </row>
     <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>6</v>
@@ -3180,19 +3184,19 @@
     </row>
     <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>6</v>
@@ -3200,19 +3204,19 @@
     </row>
     <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -3220,36 +3224,36 @@
     </row>
     <row r="78" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>179</v>
+        <v>405</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>6</v>
@@ -3260,16 +3264,16 @@
     </row>
     <row r="80" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>181</v>
+        <v>407</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>6</v>
@@ -3280,16 +3284,16 @@
     </row>
     <row r="81" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>6</v>
@@ -3300,16 +3304,16 @@
     </row>
     <row r="82" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>6</v>
@@ -3320,16 +3324,16 @@
     </row>
     <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>187</v>
+        <v>410</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>6</v>
@@ -3340,16 +3344,16 @@
     </row>
     <row r="84" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>6</v>
@@ -3360,16 +3364,16 @@
     </row>
     <row r="85" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>412</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>6</v>
@@ -3380,16 +3384,16 @@
     </row>
     <row r="86" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>6</v>
@@ -3400,19 +3404,19 @@
     </row>
     <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3420,59 +3424,59 @@
     </row>
     <row r="88" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3480,19 +3484,19 @@
     </row>
     <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3500,19 +3504,19 @@
     </row>
     <row r="92" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3520,19 +3524,19 @@
     </row>
     <row r="93" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3540,19 +3544,19 @@
     </row>
     <row r="94" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3560,16 +3564,16 @@
     </row>
     <row r="95" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>6</v>
@@ -3580,16 +3584,16 @@
     </row>
     <row r="96" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>6</v>
@@ -3600,19 +3604,19 @@
     </row>
     <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -3620,19 +3624,19 @@
     </row>
     <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -3640,19 +3644,19 @@
     </row>
     <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -3660,19 +3664,19 @@
     </row>
     <row r="100" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -3680,19 +3684,19 @@
     </row>
     <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -3700,19 +3704,19 @@
     </row>
     <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -3720,19 +3724,19 @@
     </row>
     <row r="103" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>6</v>
@@ -3740,19 +3744,19 @@
     </row>
     <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3760,19 +3764,19 @@
     </row>
     <row r="105" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3780,19 +3784,19 @@
     </row>
     <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3800,19 +3804,19 @@
     </row>
     <row r="107" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -3820,19 +3824,19 @@
     </row>
     <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -3840,19 +3844,19 @@
     </row>
     <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -3860,19 +3864,19 @@
     </row>
     <row r="110" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -3880,19 +3884,19 @@
     </row>
     <row r="111" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3900,19 +3904,19 @@
     </row>
     <row r="112" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3920,19 +3924,19 @@
     </row>
     <row r="113" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3940,19 +3944,19 @@
     </row>
     <row r="114" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3960,19 +3964,19 @@
     </row>
     <row r="115" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3980,16 +3984,16 @@
     </row>
     <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>6</v>
@@ -4000,19 +4004,19 @@
     </row>
     <row r="117" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -4020,16 +4024,16 @@
     </row>
     <row r="118" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>6</v>
@@ -4040,19 +4044,19 @@
     </row>
     <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -4060,19 +4064,19 @@
     </row>
     <row r="120" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -4080,19 +4084,19 @@
     </row>
     <row r="121" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -4100,19 +4104,19 @@
     </row>
     <row r="122" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -4120,19 +4124,19 @@
     </row>
     <row r="123" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -4140,19 +4144,19 @@
     </row>
     <row r="124" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -4160,19 +4164,19 @@
     </row>
     <row r="125" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -4180,19 +4184,19 @@
     </row>
     <row r="126" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -4200,19 +4204,19 @@
     </row>
     <row r="127" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>6</v>
@@ -4220,19 +4224,19 @@
     </row>
     <row r="128" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>6</v>
@@ -4240,19 +4244,19 @@
     </row>
     <row r="129" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>6</v>
@@ -4260,19 +4264,19 @@
     </row>
     <row r="130" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>6</v>
@@ -4280,36 +4284,36 @@
     </row>
     <row r="131" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>6</v>
@@ -4320,16 +4324,16 @@
     </row>
     <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>6</v>
@@ -4340,36 +4344,36 @@
     </row>
     <row r="134" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>6</v>
@@ -4380,36 +4384,36 @@
     </row>
     <row r="136" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>308</v>
+        <v>423</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>310</v>
+        <v>424</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>6</v>
@@ -4420,36 +4424,36 @@
     </row>
     <row r="138" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="F138" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>6</v>
@@ -4460,19 +4464,19 @@
     </row>
     <row r="140" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4480,19 +4484,19 @@
     </row>
     <row r="141" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4500,19 +4504,19 @@
     </row>
     <row r="142" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4520,19 +4524,19 @@
     </row>
     <row r="143" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4540,19 +4544,19 @@
     </row>
     <row r="144" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4560,19 +4564,19 @@
     </row>
     <row r="145" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4580,19 +4584,19 @@
     </row>
     <row r="146" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4600,59 +4604,59 @@
     </row>
     <row r="147" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>339</v>
+        <v>428</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4660,19 +4664,19 @@
     </row>
     <row r="150" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4680,19 +4684,19 @@
     </row>
     <row r="151" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4700,19 +4704,19 @@
     </row>
     <row r="152" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4720,16 +4724,16 @@
     </row>
     <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>6</v>
@@ -4740,36 +4744,36 @@
     </row>
     <row r="154" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>6</v>
@@ -4780,16 +4784,16 @@
     </row>
     <row r="156" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>354</v>
+        <v>433</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>6</v>
@@ -4800,19 +4804,19 @@
     </row>
     <row r="157" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>6</v>
@@ -4820,19 +4824,19 @@
     </row>
     <row r="158" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D158" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -4840,19 +4844,19 @@
     </row>
     <row r="159" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>6</v>
@@ -4860,19 +4864,19 @@
     </row>
     <row r="160" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>6</v>
@@ -4880,16 +4884,16 @@
     </row>
     <row r="161" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>6</v>

--- a/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3B9966-3308-4897-94B4-1FB6DA845AA6}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="6432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10752" yWindow="756" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3B9966-3308-4897-94B4-1FB6DA845AA6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10752" yWindow="756" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12084" yWindow="2064" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1140,27 +1140,6 @@
     <t>PHY212/217, MAT105/103/152</t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSC141, LSC142 (or LFS151, LFS152  AND CHE114 (or CHE124, CHE116, CHM126 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
     <t xml:space="preserve">CHE114/124, LSC141/142 (or LFS/MBS equivalents </t>
   </si>
   <si>
@@ -1170,117 +1149,42 @@
     <t xml:space="preserve">CHE114/124, LSC141/142 (or equivalents </t>
   </si>
   <si>
-    <t xml:space="preserve">Bachelor of Pharmacy  3305 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biotechnology  3211 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 114 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,Bachelor of Pharmacy  3305 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 116 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 124 (N </t>
   </si>
   <si>
     <t xml:space="preserve">Chemistry 126 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECO151 (or ECO241 </t>
   </si>
   <si>
     <t xml:space="preserve">ECO152 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Environment and Water Science  3331 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Life Sciences 151 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Life Sciences 152 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mathematics 115 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,Bachelor of Pharmacy  3305 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mathematics 151 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
     <t xml:space="preserve">MAT105 (or equivalent </t>
   </si>
   <si>
     <t xml:space="preserve">APM112, MAT105 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
     <t xml:space="preserve">CHE114, CHE124, PCH233/ (min 40% in PCH233 </t>
   </si>
   <si>
@@ -1293,49 +1197,145 @@
     <t xml:space="preserve">PHC213, PHC223, PHC313/ (min 40% for PHC313 </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Physics 151 (SF </t>
   </si>
   <si>
     <t xml:space="preserve">Physics 152 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
     <t xml:space="preserve">PCE231, PHC213, PPR214/ (min 40% in each </t>
   </si>
   <si>
     <t xml:space="preserve">PPR214, PPR224, PPR314 (min 40% </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">STA111/125/151 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Statistics 151 (SF </t>
   </si>
   <si>
-    <t>MAT105 (or equivalent  AND STA111/125/151</t>
-  </si>
-  <si>
     <t xml:space="preserve">STA211 (qualified for exam </t>
   </si>
   <si>
     <t xml:space="preserve"> General Science Elective </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Environment and Water Science 3331 ,BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology 3217 ,BSc Environment and Water Science 3331 ,BSc Biodiversity and Conservation Biology Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSC141, LSC142 (or LFS151, LFS152 AND CHE114 (or CHE124, CHE116, CHM126 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology 3217 ,BSc Biodiversity and Conservation Biology Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor of Pharmacy 3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology 3211 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Physical Science 3233 ,Bachelor of Pharmacy 3305 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Physical Science 3233 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Physical Science 3233 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Environment and Water Science 3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Environment and Water Science 3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,Bachelor of Pharmacy 3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t>MAT105 (or equivalent AND STA111/125/151</t>
   </si>
 </sst>
 </file>
@@ -1406,10 +1406,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1713,7 +1709,7 @@
         <v>354</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -1733,7 +1729,7 @@
         <v>354</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1753,7 +1749,7 @@
         <v>354</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
@@ -1773,7 +1769,7 @@
         <v>355</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1793,7 +1789,7 @@
         <v>355</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
@@ -1813,7 +1809,7 @@
         <v>355</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -1833,7 +1829,7 @@
         <v>355</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1853,7 +1849,7 @@
         <v>356</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>6</v>
@@ -1873,7 +1869,7 @@
         <v>356</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>6</v>
@@ -1893,7 +1889,7 @@
         <v>354</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -1913,7 +1909,7 @@
         <v>354</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
@@ -1933,7 +1929,7 @@
         <v>354</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
@@ -1953,10 +1949,10 @@
         <v>354</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -1973,7 +1969,7 @@
         <v>355</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>34</v>
@@ -1993,7 +1989,7 @@
         <v>355</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2013,7 +2009,7 @@
         <v>355</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -2033,7 +2029,7 @@
         <v>355</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>49</v>
@@ -2053,10 +2049,10 @@
         <v>354</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -2073,10 +2069,10 @@
         <v>354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -2093,10 +2089,10 @@
         <v>354</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -2113,7 +2109,7 @@
         <v>354</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>6</v>
@@ -2133,10 +2129,10 @@
         <v>354</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -2153,10 +2149,10 @@
         <v>354</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -2173,10 +2169,10 @@
         <v>354</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -2193,7 +2189,7 @@
         <v>355</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>66</v>
@@ -2213,7 +2209,7 @@
         <v>355</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -2233,7 +2229,7 @@
         <v>355</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>66</v>
@@ -2253,7 +2249,7 @@
         <v>355</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>66</v>
@@ -2267,13 +2263,13 @@
         <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>6</v>
@@ -2287,13 +2283,13 @@
         <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>6</v>
@@ -2307,13 +2303,13 @@
         <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>6</v>
@@ -2327,13 +2323,13 @@
         <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>6</v>
@@ -2353,7 +2349,7 @@
         <v>354</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>79</v>
@@ -2373,7 +2369,7 @@
         <v>354</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>79</v>
@@ -2393,7 +2389,7 @@
         <v>354</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>79</v>
@@ -2413,7 +2409,7 @@
         <v>355</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>86</v>
@@ -2433,7 +2429,7 @@
         <v>355</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>86</v>
@@ -2453,7 +2449,7 @@
         <v>355</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>91</v>
@@ -2473,7 +2469,7 @@
         <v>355</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>91</v>
@@ -2493,7 +2489,7 @@
         <v>356</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>6</v>
@@ -2513,7 +2509,7 @@
         <v>356</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>6</v>
@@ -2533,7 +2529,7 @@
         <v>356</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>6</v>
@@ -2553,7 +2549,7 @@
         <v>354</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>94</v>
@@ -2573,7 +2569,7 @@
         <v>354</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>94</v>
@@ -2593,7 +2589,7 @@
         <v>355</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>106</v>
@@ -2613,7 +2609,7 @@
         <v>355</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>106</v>
@@ -2633,7 +2629,7 @@
         <v>356</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>6</v>
@@ -2653,7 +2649,7 @@
         <v>356</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>6</v>
@@ -2673,10 +2669,10 @@
         <v>354</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2693,10 +2689,10 @@
         <v>354</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2713,10 +2709,10 @@
         <v>354</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2733,7 +2729,7 @@
         <v>354</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>357</v>
@@ -2753,7 +2749,7 @@
         <v>355</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>119</v>
@@ -2773,7 +2769,7 @@
         <v>355</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>113</v>
@@ -2793,7 +2789,7 @@
         <v>355</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>115</v>
@@ -2813,7 +2809,7 @@
         <v>355</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>129</v>
@@ -2833,7 +2829,7 @@
         <v>355</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>129</v>
@@ -2853,7 +2849,7 @@
         <v>355</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>115</v>
@@ -2873,7 +2869,7 @@
         <v>356</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>6</v>
@@ -2893,7 +2889,7 @@
         <v>356</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>6</v>
@@ -2913,7 +2909,7 @@
         <v>356</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>6</v>
@@ -2933,7 +2929,7 @@
         <v>356</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>6</v>
@@ -2953,7 +2949,7 @@
         <v>354</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>9</v>
@@ -2973,7 +2969,7 @@
         <v>354</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>9</v>
@@ -2993,7 +2989,7 @@
         <v>354</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>9</v>
@@ -3013,7 +3009,7 @@
         <v>355</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>151</v>
@@ -3033,7 +3029,7 @@
         <v>355</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>151</v>
@@ -3053,7 +3049,7 @@
         <v>355</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>148</v>
@@ -3073,7 +3069,7 @@
         <v>355</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>151</v>
@@ -3093,7 +3089,7 @@
         <v>356</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>6</v>
@@ -3113,7 +3109,7 @@
         <v>356</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>6</v>
@@ -3133,7 +3129,7 @@
         <v>356</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>6</v>
@@ -3153,7 +3149,7 @@
         <v>354</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>358</v>
@@ -3173,7 +3169,7 @@
         <v>354</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>164</v>
@@ -3193,7 +3189,7 @@
         <v>355</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>359</v>
@@ -3213,7 +3209,7 @@
         <v>355</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>168</v>
@@ -3233,7 +3229,7 @@
         <v>356</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>6</v>
@@ -3247,13 +3243,13 @@
         <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>6</v>
@@ -3267,13 +3263,13 @@
         <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>6</v>
@@ -3293,7 +3289,7 @@
         <v>356</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>6</v>
@@ -3313,7 +3309,7 @@
         <v>356</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>6</v>
@@ -3327,13 +3323,13 @@
         <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>6</v>
@@ -3353,7 +3349,7 @@
         <v>356</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>6</v>
@@ -3367,13 +3363,13 @@
         <v>182</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>6</v>
@@ -3393,7 +3389,7 @@
         <v>356</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>6</v>
@@ -3413,10 +3409,10 @@
         <v>354</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3433,10 +3429,10 @@
         <v>354</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>185</v>
@@ -3453,7 +3449,7 @@
         <v>354</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>6</v>
@@ -3473,10 +3469,10 @@
         <v>354</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3493,7 +3489,7 @@
         <v>355</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>185</v>
@@ -3513,7 +3509,7 @@
         <v>355</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>197</v>
@@ -3533,7 +3529,7 @@
         <v>355</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>189</v>
@@ -3553,7 +3549,7 @@
         <v>355</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>197</v>
@@ -3573,7 +3569,7 @@
         <v>356</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>6</v>
@@ -3593,7 +3589,7 @@
         <v>356</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>6</v>
@@ -3613,7 +3609,7 @@
         <v>354</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>208</v>
@@ -3633,7 +3629,7 @@
         <v>354</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>208</v>
@@ -3653,7 +3649,7 @@
         <v>355</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>362</v>
@@ -3673,7 +3669,7 @@
         <v>355</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>363</v>
@@ -3693,7 +3689,7 @@
         <v>354</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>176</v>
@@ -3713,7 +3709,7 @@
         <v>354</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>215</v>
@@ -3733,7 +3729,7 @@
         <v>355</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>364</v>
@@ -3753,7 +3749,7 @@
         <v>355</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>364</v>
@@ -3773,7 +3769,7 @@
         <v>354</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>225</v>
@@ -3793,7 +3789,7 @@
         <v>354</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>225</v>
@@ -3813,7 +3809,7 @@
         <v>355</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>230</v>
@@ -3833,7 +3829,7 @@
         <v>355</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>233</v>
@@ -3853,7 +3849,7 @@
         <v>365</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>236</v>
@@ -3873,7 +3869,7 @@
         <v>365</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>236</v>
@@ -3893,10 +3889,10 @@
         <v>354</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3913,7 +3909,7 @@
         <v>354</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>79</v>
@@ -3933,7 +3929,7 @@
         <v>355</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>245</v>
@@ -3953,10 +3949,10 @@
         <v>355</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3973,7 +3969,7 @@
         <v>365</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>250</v>
@@ -3993,7 +3989,7 @@
         <v>356</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>6</v>
@@ -4013,7 +4009,7 @@
         <v>365</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>255</v>
@@ -4033,7 +4029,7 @@
         <v>365</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>6</v>
@@ -4053,7 +4049,7 @@
         <v>365</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>260</v>
@@ -4073,7 +4069,7 @@
         <v>356</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>160</v>
@@ -4093,7 +4089,7 @@
         <v>354</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>265</v>
@@ -4113,10 +4109,10 @@
         <v>354</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -4133,7 +4129,7 @@
         <v>355</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>270</v>
@@ -4153,10 +4149,10 @@
         <v>355</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -4173,7 +4169,7 @@
         <v>365</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>275</v>
@@ -4193,7 +4189,7 @@
         <v>365</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>255</v>
@@ -4213,7 +4209,7 @@
         <v>365</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>280</v>
@@ -4233,7 +4229,7 @@
         <v>365</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>283</v>
@@ -4253,7 +4249,7 @@
         <v>365</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>286</v>
@@ -4273,7 +4269,7 @@
         <v>365</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>275</v>
@@ -4293,7 +4289,7 @@
         <v>356</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>6</v>
@@ -4313,7 +4309,7 @@
         <v>356</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>6</v>
@@ -4333,7 +4329,7 @@
         <v>356</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>6</v>
@@ -4353,7 +4349,7 @@
         <v>356</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>6</v>
@@ -4373,7 +4369,7 @@
         <v>356</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>6</v>
@@ -4387,13 +4383,13 @@
         <v>299</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>6</v>
@@ -4407,13 +4403,13 @@
         <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>6</v>
@@ -4433,7 +4429,7 @@
         <v>354</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>367</v>
@@ -4453,7 +4449,7 @@
         <v>354</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>6</v>
@@ -4473,7 +4469,7 @@
         <v>354</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>368</v>
@@ -4493,7 +4489,7 @@
         <v>354</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>369</v>
@@ -4513,7 +4509,7 @@
         <v>355</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>312</v>
@@ -4533,7 +4529,7 @@
         <v>355</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>308</v>
@@ -4553,7 +4549,7 @@
         <v>355</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>312</v>
@@ -4573,7 +4569,7 @@
         <v>355</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>370</v>
@@ -4593,7 +4589,7 @@
         <v>354</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>321</v>
@@ -4613,10 +4609,10 @@
         <v>354</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>266</v>
@@ -4633,7 +4629,7 @@
         <v>355</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>326</v>
@@ -4653,10 +4649,10 @@
         <v>355</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4673,7 +4669,7 @@
         <v>365</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>331</v>
@@ -4693,7 +4689,7 @@
         <v>365</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>331</v>
@@ -4713,7 +4709,7 @@
         <v>365</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>331</v>
@@ -4733,7 +4729,7 @@
         <v>356</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>6</v>
@@ -4753,13 +4749,13 @@
         <v>356</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -4773,7 +4769,7 @@
         <v>356</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>6</v>
@@ -4787,13 +4783,13 @@
         <v>342</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>6</v>
@@ -4813,10 +4809,10 @@
         <v>354</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>6</v>
@@ -4833,10 +4829,10 @@
         <v>354</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -4853,7 +4849,7 @@
         <v>355</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>349</v>
@@ -4873,7 +4869,7 @@
         <v>355</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>349</v>
@@ -4893,7 +4889,7 @@
         <v>356</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>436</v>
+        <v>397</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>6</v>

--- a/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942A8FA9-F9D3-439D-94B3-89898E30665B}"/>
   <bookViews>
-    <workbookView xWindow="12084" yWindow="2064" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Undergrad Modules Natural Science.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942A8FA9-F9D3-439D-94B3-89898E30665B}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B27A5E69-7B67-4C43-96A4-217930072E06}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="683">
   <si>
     <t>Module code</t>
   </si>
@@ -1336,14 +1336,856 @@
   </si>
   <si>
     <t>MAT105 (or equivalent AND STA111/125/151</t>
+  </si>
+  <si>
+    <t>Learning Outcome</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>Main Content</t>
+  </si>
+  <si>
+    <t>Identify crystal forms/systems; describe mineral properties; explain geochemistry principles and sedimentary processes.</t>
+  </si>
+  <si>
+    <t>Crystallography; mineral classification; atomic theory; bonding; geochemical principles; sedimentary rock classification.</t>
+  </si>
+  <si>
+    <t>Understand map construction, rock deformation, and light propagation; use polarized-light microscopes.</t>
+  </si>
+  <si>
+    <t>Geological map reading; cross-sections; stress and strain concepts; microscopic mineral identification.</t>
+  </si>
+  <si>
+    <t>Observe/describe field rock occurrences; locate self in field; produce geological maps and take measurements.</t>
+  </si>
+  <si>
+    <t>Characterization and mapping of igneous/metamorphic rocks; structural measurements; report production.</t>
+  </si>
+  <si>
+    <t>Outline petroleum history; assess hydrocarbon accumulation; categorize depositional environments; analyze sedimentary systems.</t>
+  </si>
+  <si>
+    <t>Petroleum evolution; facies analysis; depositional systems; well logs; seismic exploration; reservoir modeling.</t>
+  </si>
+  <si>
+    <t>Evaluate igneous/metamorphic rock origins and textures; relate mineralogy to chemistry; interpret phase diagrams.</t>
+  </si>
+  <si>
+    <t>Igneous and metamorphic rock-forming processes; phase diagrams; origin and evolution of rock types.</t>
+  </si>
+  <si>
+    <t>Reflect on Earth's interior dynamics; evaluate tectonics and ore deposit formation; analyze geochemical data.</t>
+  </si>
+  <si>
+    <t>Plate tectonics; Wilson cycle; structural analysis; genetic classification of ore deposits; exploration geochemistry.</t>
+  </si>
+  <si>
+    <t>Apply spatial techniques in geology; analyze interpretation of geospatial data; integrate data into computer models.</t>
+  </si>
+  <si>
+    <t>GIS concepts; cartography; geodatabases; 2D/3D modelling; satellite imagery; field mapping.</t>
+  </si>
+  <si>
+    <t>Apply mathematical methods and techniques in Physical Sciences.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to Faculty of Natural Sciences descriptors (Mathematics and Applied Mathematics)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Refer to Faculty of Natural Sciences descriptors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Compulsory module in Biodiversity stream.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 211.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 221.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 222.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 223.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 332.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 333.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 334.</t>
+  </si>
+  <si>
+    <t>Biodiversity and Conservation Biology 335.</t>
+  </si>
+  <si>
+    <t>Compulsory module in Biotechnology stream.</t>
+  </si>
+  <si>
+    <t>Biotechnology 211.</t>
+  </si>
+  <si>
+    <t>Elective module in Biotechnology stream.</t>
+  </si>
+  <si>
+    <t>Biotechnology 213.</t>
+  </si>
+  <si>
+    <t>Biotechnology 215.</t>
+  </si>
+  <si>
+    <t>Compulsory module in Pharmacy stream.</t>
+  </si>
+  <si>
+    <t>Biotechnology 217.</t>
+  </si>
+  <si>
+    <t>Biotechnology 218.</t>
+  </si>
+  <si>
+    <t>Biotechnology 222.</t>
+  </si>
+  <si>
+    <t>Biotechnology 223.</t>
+  </si>
+  <si>
+    <t>Biotechnology 312.</t>
+  </si>
+  <si>
+    <t>Biotechnology 315.</t>
+  </si>
+  <si>
+    <t>Biotechnology 316.</t>
+  </si>
+  <si>
+    <t>Biotechnology 322.</t>
+  </si>
+  <si>
+    <t>Apply chemical concepts to naming, forces, stability, and rates of change qualitatively.</t>
+  </si>
+  <si>
+    <t>Chemistry 114 (N).</t>
+  </si>
+  <si>
+    <t>Chemistry 116 (N).</t>
+  </si>
+  <si>
+    <t>Apply chemical concepts to real-world phenomena regarding naming, stability, and chemical change.</t>
+  </si>
+  <si>
+    <t>Chemistry 124 (N).</t>
+  </si>
+  <si>
+    <t>Chemistry 126 (N).</t>
+  </si>
+  <si>
+    <t>Describe atomic properties and explain periodic trends.</t>
+  </si>
+  <si>
+    <t>Aromatic chemistry; periodic table trends; transition metals; organometallic chemistry.</t>
+  </si>
+  <si>
+    <t>Use gravimetric analysis; understand pH titration and thermodynamics laws; examine chemical kinetics.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers analytical and physical chemistry principles).</t>
+  </si>
+  <si>
+    <t>Compulsory module in Level 2.</t>
+  </si>
+  <si>
+    <t>Chemistry 221.</t>
+  </si>
+  <si>
+    <t>Classify organic rearrangements;Synthetic protocols; examine bonding in co-ordination chemistry.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers organic and inorganic chemistry).</t>
+  </si>
+  <si>
+    <t>Use principles of chemical processes; demonstrate corrosion control and electrochemistry role in energy.</t>
+  </si>
+  <si>
+    <t>Types of chemical industries; process design; raw materials; industrial processes.</t>
+  </si>
+  <si>
+    <t>Compulsory module in Level 3.</t>
+  </si>
+  <si>
+    <t>Chemistry 321.</t>
+  </si>
+  <si>
+    <t>Chemistry 322.</t>
+  </si>
+  <si>
+    <t>Apply problem solving; design algorithms in Java; understand SDLC and OO paradigm.</t>
+  </si>
+  <si>
+    <t>Algorithm design; pseudocode; high-level programming; OO design.</t>
+  </si>
+  <si>
+    <t>Use computers/internet; use worksheets/databases; understand file organization.</t>
+  </si>
+  <si>
+    <t>Computing Fundamentals 114.</t>
+  </si>
+  <si>
+    <t>Computing Fundamentals 124.</t>
+  </si>
+  <si>
+    <t>Implement algorithms; derive time/space complexity; procedural/OO problem solving.</t>
+  </si>
+  <si>
+    <t>Computer Science 211.</t>
+  </si>
+  <si>
+    <t>Explain algorithm efficiency and intractable problems; low- and high-level software interaction.</t>
+  </si>
+  <si>
+    <t>Computer Science 212.</t>
+  </si>
+  <si>
+    <t>Computer Science 311.</t>
+  </si>
+  <si>
+    <t>Computer Science 312.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to Faculty of Economic and Management Sciences Calendar for outcomes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Introduction to Microeconomics 151.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to Faculty of EMS Calendar for outcomes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Introduction to Macroeconomics 152.</t>
+  </si>
+  <si>
+    <t>Microeconomics 231.</t>
+  </si>
+  <si>
+    <t>Macroeconomics 232.</t>
+  </si>
+  <si>
+    <t>Intermediate Mathematical Economics 235.</t>
+  </si>
+  <si>
+    <t>Econometrics 242.</t>
+  </si>
+  <si>
+    <t>Econometrics 311.</t>
+  </si>
+  <si>
+    <t>Microeconomics 331.</t>
+  </si>
+  <si>
+    <t>Macroeconomics 332.</t>
+  </si>
+  <si>
+    <t>Public Sector Economics 334.</t>
+  </si>
+  <si>
+    <t>Critically evaluate neoclassical trade theory; apply new trade theory; use graphical analysis.</t>
+  </si>
+  <si>
+    <t>Classical/neoclassical trade theory; tariffs; imperfect competition; economic integration.</t>
+  </si>
+  <si>
+    <t>Model development economics concepts; analyze developing countries; interpret statistical data.</t>
+  </si>
+  <si>
+    <t>Poverty and inequality; growth experiences; agrarian change; capital flows.</t>
+  </si>
+  <si>
+    <t>Research topics using databases; integrate research into writing; write argumentative essays/IMRaD.</t>
+  </si>
+  <si>
+    <t>English for Educational Development 117.</t>
+  </si>
+  <si>
+    <t>(Similar to EED117).</t>
+  </si>
+  <si>
+    <t>English for Educational Development 127.</t>
+  </si>
+  <si>
+    <t>Explain basic Earth Materials; identify rocks/minerals; grasp stratigraphy and Earth dynamics.</t>
+  </si>
+  <si>
+    <t>Structure of Earth; Rock Cycle; Geology of SA; structural geology and mapping.</t>
+  </si>
+  <si>
+    <t>Understand origins of Earth system cycles; synthesise theories; source literature; write academic essays.</t>
+  </si>
+  <si>
+    <t>Atmosphere; global radiation balance; climate; weathering; hydrological cycle; biome distribution.</t>
+  </si>
+  <si>
+    <t>Identify and describe hydrological processes; explain spatial/temporal variation.</t>
+  </si>
+  <si>
+    <t>Environmental and Water Science 211.</t>
+  </si>
+  <si>
+    <t>Describe hydro-geologic systems; explain groundwater hydraulics/chemistry; identify water interactions.</t>
+  </si>
+  <si>
+    <t>Hydro-geologic system; flow mechanisms; water quality; groundwater dependent ecosystems.</t>
+  </si>
+  <si>
+    <t>Select and apply field methods/equipment; analyze parameters; scientific report writing.</t>
+  </si>
+  <si>
+    <t>Field-based sampling; parameter reporting; data analysis methods.</t>
+  </si>
+  <si>
+    <t>Demonstrate spatial data query and analysis using GIS tools.</t>
+  </si>
+  <si>
+    <t>GIS data/analysis; cartography; statistical data analysis; natural resource studies.</t>
+  </si>
+  <si>
+    <t>Apply aquifer characterisation; evaluate groundwater hydraulics; simulate flow-dynamics.</t>
+  </si>
+  <si>
+    <t>Hydrological variability; surface water; river flow; aquifer characterisation; groundwater modelling.</t>
+  </si>
+  <si>
+    <t>Analyze environmental/water resource management concepts; apply IWRM; addressing SDGs.</t>
+  </si>
+  <si>
+    <t>Environmental management; sustainable development; SA water policy; NWRS; IWRM concepts.</t>
+  </si>
+  <si>
+    <t>Environmental and Water Science 322.</t>
+  </si>
+  <si>
+    <t>Describe structure/function of proteins, carbohydrates, lipids; explain nutrition/metabolism.</t>
+  </si>
+  <si>
+    <t>Chemical compounds; digestive system; early development; skeletal/muscle systems.</t>
+  </si>
+  <si>
+    <t>Compulsory module in Level 1.</t>
+  </si>
+  <si>
+    <t>Human Biology 123.</t>
+  </si>
+  <si>
+    <t>Elective module in Level 1.</t>
+  </si>
+  <si>
+    <t>Information Systems 132.</t>
+  </si>
+  <si>
+    <t>Analyze business requirements and processes; identify stakeholder solutions; analyze SDLC.</t>
+  </si>
+  <si>
+    <t>Function of analyst; solution design; foundations of data modelling; trending concepts.</t>
+  </si>
+  <si>
+    <t>Apply project management fundamental concepts (scope, time, budget, risk); evaluate methodologies.</t>
+  </si>
+  <si>
+    <t>Relational/OO databases; data modelling; UML; OO design/development lifecycle.</t>
+  </si>
+  <si>
+    <t>Requirements analysis; design/build/test; security techniques; collaboration tools.</t>
+  </si>
+  <si>
+    <t>Information Systems 317.</t>
+  </si>
+  <si>
+    <t>Introduction to Science for Extended Curriculum.</t>
+  </si>
+  <si>
+    <t>(Foundational science content).</t>
+  </si>
+  <si>
+    <t>Compulsory module in SF Level 1.</t>
+  </si>
+  <si>
+    <t>Life Sciences 151 (SF).</t>
+  </si>
+  <si>
+    <t>Compulsory module in SF Level 2.</t>
+  </si>
+  <si>
+    <t>Life Sciences 152 (SF).</t>
+  </si>
+  <si>
+    <t>Link inorganic chemistry to cell organisation; maintenance of life molecules; explain organelle interaction.</t>
+  </si>
+  <si>
+    <t>Origin of living cells; evolution of higher life.</t>
+  </si>
+  <si>
+    <t>Use basic rules to classify/describe/identify life; write basic scientific reports.</t>
+  </si>
+  <si>
+    <t>History of life; diversity (bacteria to viruses); levels of ecology; human impact on biodiversity.</t>
+  </si>
+  <si>
+    <t>Mathematics 115 (N).</t>
+  </si>
+  <si>
+    <t>Introduction to Mathematics 150.</t>
+  </si>
+  <si>
+    <t>Mathematics 151 (SF).</t>
+  </si>
+  <si>
+    <t>Implement methods of Differential/Integral calculus in Life Sciences and Pharmacy.</t>
+  </si>
+  <si>
+    <t>introduction to math language; functions (polynomial, rational); graphs; absolute value.</t>
+  </si>
+  <si>
+    <t>Mathematics 211.</t>
+  </si>
+  <si>
+    <t>Elective module in Level 2.</t>
+  </si>
+  <si>
+    <t>Mathematics 212.</t>
+  </si>
+  <si>
+    <t>Mathematics 221.</t>
+  </si>
+  <si>
+    <t>Solve set theory/logic problems; use combinatorial techniques; solve counting problems in graph theory.</t>
+  </si>
+  <si>
+    <t>Axiomatic set theory and logic; enumerative combinatorics; introductory graph theory.</t>
+  </si>
+  <si>
+    <t>Mathematics 311.</t>
+  </si>
+  <si>
+    <t>Analyse/simulate models for population systems; stability analysis; find equilibrium.</t>
+  </si>
+  <si>
+    <t>Predator-prey models; epidemiology fundamentals; optimal control problems.</t>
+  </si>
+  <si>
+    <t>Use theory of groups; carry out proofs; generalize to Rings; construct finite fields.</t>
+  </si>
+  <si>
+    <t>(Advanced abstract algebra).</t>
+  </si>
+  <si>
+    <t>Implement geometric Brownian motion; use pricing via arbitrage; use vanilla/exotic options.</t>
+  </si>
+  <si>
+    <t>(Financial mathematics tools).</t>
+  </si>
+  <si>
+    <t>Compulsory module in Medical stream.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 111.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 121.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 231.</t>
+  </si>
+  <si>
+    <t>Knowledge of macro- and microscopic structures.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 232.</t>
+  </si>
+  <si>
+    <t>Compulsory module in Level 4.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 331.</t>
+  </si>
+  <si>
+    <t>Medical Biosciences 332.</t>
+  </si>
+  <si>
+    <t>Medical Microbiology 251.</t>
+  </si>
+  <si>
+    <t>Medical Microbiology 252.</t>
+  </si>
+  <si>
+    <t>Medical Microbiology 353.</t>
+  </si>
+  <si>
+    <t>Medical Microbiology 354.</t>
+  </si>
+  <si>
+    <t>Explain GMP principles; identify dosage forms; use reference sources.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers pharmaceutics foundations).</t>
+  </si>
+  <si>
+    <t>Explain disperse system stability; physicochemical manipulation; explain rheological properties.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers product stability).</t>
+  </si>
+  <si>
+    <t>Compulsory Pharmacy module.</t>
+  </si>
+  <si>
+    <t>Pharmaceutics 331.</t>
+  </si>
+  <si>
+    <t>Pharmaceutics 333.</t>
+  </si>
+  <si>
+    <t>Elective Pharmacy module.</t>
+  </si>
+  <si>
+    <t>Pharmaceutics 401.</t>
+  </si>
+  <si>
+    <t>Pharmaceutics 431.</t>
+  </si>
+  <si>
+    <t>Describe therapeutic value of plants; identify medicinal plants or crude drugs.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers pharmaceutical chemistry of plants).</t>
+  </si>
+  <si>
+    <t>Describe principles in analysis and quality control of drugs.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers drug quality control).</t>
+  </si>
+  <si>
+    <t>Pharmaceutical Chemistry 312.</t>
+  </si>
+  <si>
+    <t>Pharmaceutical Chemistry 322.</t>
+  </si>
+  <si>
+    <t>Pharmaceutical Chemistry 402.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to Faculty of Community and Health Sciences Calendar for outcomes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Main content restricted - consult School of Pharmacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Understand research methods; plan/conduct project; write up results; oral presentation.</t>
+  </si>
+  <si>
+    <t>Research proposal structure; project execution; results write-up.</t>
+  </si>
+  <si>
+    <t>Pharmacy 426.</t>
+  </si>
+  <si>
+    <t>Community Engagement 427.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 123.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 213.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 223.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 313.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 323.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 403.</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 405.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to School of Pharmacy Home Department</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>(Level 4 Pharm focus).</t>
+  </si>
+  <si>
+    <t>(Check)</t>
+  </si>
+  <si>
+    <t>Demonstrate cultural competence via communication skills.</t>
+  </si>
+  <si>
+    <t>Global Pharmacy.</t>
+  </si>
+  <si>
+    <t>Discuss rational medicine use; apply quantitative methods; describe evidence based medicine.</t>
+  </si>
+  <si>
+    <t>(Descriptor covers systems for rational medicine use).</t>
+  </si>
+  <si>
+    <t>Pharmacology and Clinical Pharmacy 426.</t>
+  </si>
+  <si>
+    <t>Work and energy; impulse and momentum; rotational equilibrium.</t>
+  </si>
+  <si>
+    <t>Discuss mechanics, hydrostatics, and electricity; solve qualitative/quantitative problems; lab work.</t>
+  </si>
+  <si>
+    <t>Science as way of knowing; vectors; equilibrium; elasticity; hydrostatics; dental/pharmacy apps.</t>
+  </si>
+  <si>
+    <t>Apply scientific approach; understand technologies via modern physics and thermodynamics.</t>
+  </si>
+  <si>
+    <t>Physics 116 (N).</t>
+  </si>
+  <si>
+    <t>Understand wave phenomena and magnetism; apply concepts of vibrations and waves; work in lab.</t>
+  </si>
+  <si>
+    <t>Gravitational forces; satellite motion; work and energy; impulse and momentum.</t>
+  </si>
+  <si>
+    <t>Physics 126 (N).</t>
+  </si>
+  <si>
+    <t>Physics 151 (SF).</t>
+  </si>
+  <si>
+    <t>Physics 152 (SF).</t>
+  </si>
+  <si>
+    <t>Basic computational physics; laboratory experiments.</t>
+  </si>
+  <si>
+    <t>Physics 217.</t>
+  </si>
+  <si>
+    <t>Solve Classical Mechanics and Electrodynamics problems; utilize mathematical/computer skills.</t>
+  </si>
+  <si>
+    <t>(Physical science focus).</t>
+  </si>
+  <si>
+    <t>Describe environmental energy issues; present on energy supply; do experimental work.</t>
+  </si>
+  <si>
+    <t>(Environmental physics focus).</t>
+  </si>
+  <si>
+    <t>Quantum physics experiments; data analysis; report writing and presentation skills.</t>
+  </si>
+  <si>
+    <t>Discuss renewable energy sources; evaluate energy issues in SA; do PV systems sizing.</t>
+  </si>
+  <si>
+    <t>Renewable fuels; solar cell design; energy technology in SA; lab applications.</t>
+  </si>
+  <si>
+    <t>Apply kinetic theory of gases to matter properties on thermodynamics basis.</t>
+  </si>
+  <si>
+    <t>(Statistical mechanics focus).</t>
+  </si>
+  <si>
+    <t>Explain physics/math of astronomy ideas; operate telescopes; use computational modelling.</t>
+  </si>
+  <si>
+    <t>Spectra analysis; General relativity; astrophysical fluids; communicating ideas.</t>
+  </si>
+  <si>
+    <t>Pharmacy Practice 214.</t>
+  </si>
+  <si>
+    <t>Pharmacy Practice 224.</t>
+  </si>
+  <si>
+    <t>Pharmacy Practice 314.</t>
+  </si>
+  <si>
+    <t>Explain, interpret, and apply human resources management theories.</t>
+  </si>
+  <si>
+    <t>Pharmacy Practice 324.</t>
+  </si>
+  <si>
+    <t>Understand pharmacoeconomics role; define terminology; apply economic principles.</t>
+  </si>
+  <si>
+    <t>Pharmacoeconomic analyses/modelling; health outcomes research; drug development apps.</t>
+  </si>
+  <si>
+    <r>
+      <t>Refer to School of Pharmacy descriptors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Financial management; CPD and professional portfolio; scenario planning.</t>
+  </si>
+  <si>
+    <t>Summarize data; do simple statistical analysis; use computer for data analysis.</t>
+  </si>
+  <si>
+    <t>Descriptive statistics; linear regression; probability; inferential stats; Chi-Square.</t>
+  </si>
+  <si>
+    <t>Statistics 121.</t>
+  </si>
+  <si>
+    <t>Statistics 125.</t>
+  </si>
+  <si>
+    <t>Statistics 151 (SF).</t>
+  </si>
+  <si>
+    <t>Distribution theory; moments; sampling; reports and graphs.</t>
+  </si>
+  <si>
+    <t>Statistics 221.</t>
+  </si>
+  <si>
+    <t>Elective module in Level 3.</t>
+  </si>
+  <si>
+    <t>Statistics 331.</t>
+  </si>
+  <si>
+    <t>Execute advanced linear models; multivariate regression; execute data analysis via packages.</t>
+  </si>
+  <si>
+    <t>Advanced inference; advanced regression analysis; computer output interpretation.</t>
+  </si>
+  <si>
+    <t>Show data trends; understand statistical theory (probability, sampling); apply frequency statistics.</t>
+  </si>
+  <si>
+    <t>Population and samples; basic concepts; graphing distributions.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1386,10 +2228,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1406,6 +2257,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1671,34 +2526,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:I161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="38.88671875" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1717,8 +2581,17 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="I2" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1737,8 +2610,17 @@
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G3" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I3" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1757,8 +2639,17 @@
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I4" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1777,8 +2668,17 @@
       <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G5" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="I5" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1797,8 +2697,17 @@
       <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G6" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="I6" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1817,8 +2726,17 @@
       <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G7" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="I7" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1837,8 +2755,17 @@
       <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G8" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="I8" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1857,8 +2784,17 @@
       <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G9" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I9" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1877,8 +2813,17 @@
       <c r="F10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G10" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="I10" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1897,8 +2842,17 @@
       <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G11" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="I11" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1917,8 +2871,17 @@
       <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G12" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="I12" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1937,8 +2900,17 @@
       <c r="F13" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="G13" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="I13" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1957,8 +2929,17 @@
       <c r="F14" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G14" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="I14" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -1977,8 +2958,17 @@
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G15" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="I15" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
@@ -1997,8 +2987,17 @@
       <c r="F16" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G16" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="I16" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -2017,8 +3016,17 @@
       <c r="F17" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G17" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="I17" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>47</v>
       </c>
@@ -2037,8 +3045,17 @@
       <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G18" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I18" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -2057,8 +3074,17 @@
       <c r="F19" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G19" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="I19" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -2077,8 +3103,17 @@
       <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G20" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I20" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -2097,8 +3132,17 @@
       <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G21" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="I21" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
@@ -2117,8 +3161,17 @@
       <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G22" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="I22" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -2137,8 +3190,17 @@
       <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G23" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="I23" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>60</v>
       </c>
@@ -2157,8 +3219,17 @@
       <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G24" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="I24" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
@@ -2177,8 +3248,17 @@
       <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G25" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I25" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
@@ -2197,8 +3277,17 @@
       <c r="F26" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G26" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I26" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
@@ -2217,8 +3306,17 @@
       <c r="F27" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G27" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="I27" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>69</v>
       </c>
@@ -2237,8 +3335,17 @@
       <c r="F28" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G28" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I28" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>71</v>
       </c>
@@ -2257,8 +3364,17 @@
       <c r="F29" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G29" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="I29" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>73</v>
       </c>
@@ -2277,8 +3393,17 @@
       <c r="F30" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G30" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I30" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
@@ -2297,8 +3422,17 @@
       <c r="F31" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G31" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="I31" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>75</v>
       </c>
@@ -2317,8 +3451,17 @@
       <c r="F32" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G32" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="I32" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>76</v>
       </c>
@@ -2337,8 +3480,17 @@
       <c r="F33" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G33" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="I33" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>77</v>
       </c>
@@ -2357,8 +3509,17 @@
       <c r="F34" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G34" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="I34" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>80</v>
       </c>
@@ -2377,8 +3538,17 @@
       <c r="F35" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G35" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I35" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -2397,8 +3567,17 @@
       <c r="F36" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G36" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="I36" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>84</v>
       </c>
@@ -2417,8 +3596,17 @@
       <c r="F37" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G37" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="I37" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>87</v>
       </c>
@@ -2437,8 +3625,17 @@
       <c r="F38" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G38" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="I38" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
@@ -2457,8 +3654,17 @@
       <c r="F39" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G39" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="I39" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>92</v>
       </c>
@@ -2477,8 +3683,17 @@
       <c r="F40" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G40" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I40" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>94</v>
       </c>
@@ -2497,8 +3712,17 @@
       <c r="F41" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G41" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I41" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
@@ -2517,8 +3741,17 @@
       <c r="F42" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G42" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="I42" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
@@ -2537,8 +3770,17 @@
       <c r="F43" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G43" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="I43" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
@@ -2557,8 +3799,17 @@
       <c r="F44" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G44" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="I44" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -2577,8 +3828,17 @@
       <c r="F45" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G45" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="I45" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -2597,8 +3857,17 @@
       <c r="F46" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G46" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="I46" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>107</v>
       </c>
@@ -2617,8 +3886,17 @@
       <c r="F47" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G47" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="I47" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>109</v>
       </c>
@@ -2637,8 +3915,17 @@
       <c r="F48" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G48" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>111</v>
       </c>
@@ -2657,8 +3944,17 @@
       <c r="F49" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G49" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="I49" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>113</v>
       </c>
@@ -2677,8 +3973,17 @@
       <c r="F50" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G50" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I50" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>115</v>
       </c>
@@ -2697,8 +4002,17 @@
       <c r="F51" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G51" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I51" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>117</v>
       </c>
@@ -2717,8 +4031,17 @@
       <c r="F52" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G52" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="I52" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
@@ -2737,8 +4060,17 @@
       <c r="F53" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G53" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="I53" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>121</v>
       </c>
@@ -2757,8 +4089,17 @@
       <c r="F54" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G54" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="I54" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>123</v>
       </c>
@@ -2777,8 +4118,17 @@
       <c r="F55" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G55" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="I55" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>125</v>
       </c>
@@ -2797,8 +4147,17 @@
       <c r="F56" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G56" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="I56" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>127</v>
       </c>
@@ -2817,8 +4176,17 @@
       <c r="F57" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G57" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="I57" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>130</v>
       </c>
@@ -2837,8 +4205,17 @@
       <c r="F58" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G58" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="I58" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>132</v>
       </c>
@@ -2857,8 +4234,17 @@
       <c r="F59" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G59" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="I59" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>134</v>
       </c>
@@ -2877,8 +4263,17 @@
       <c r="F60" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G60" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="I60" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>136</v>
       </c>
@@ -2897,8 +4292,17 @@
       <c r="F61" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G61" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I61" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>138</v>
       </c>
@@ -2917,8 +4321,17 @@
       <c r="F62" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G62" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="I62" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>140</v>
       </c>
@@ -2937,8 +4350,17 @@
       <c r="F63" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G63" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="I63" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>142</v>
       </c>
@@ -2957,8 +4379,17 @@
       <c r="F64" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G64" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="I64" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>144</v>
       </c>
@@ -2977,8 +4408,17 @@
       <c r="F65" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G65" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="I65" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>146</v>
       </c>
@@ -2997,8 +4437,17 @@
       <c r="F66" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G66" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I66" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>149</v>
       </c>
@@ -3017,8 +4466,17 @@
       <c r="F67" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G67" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="I67" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>152</v>
       </c>
@@ -3037,8 +4495,17 @@
       <c r="F68" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G68" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="I68" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>154</v>
       </c>
@@ -3057,8 +4524,17 @@
       <c r="F69" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G69" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="I69" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>156</v>
       </c>
@@ -3077,8 +4553,17 @@
       <c r="F70" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G70" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="I70" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>158</v>
       </c>
@@ -3097,8 +4582,17 @@
       <c r="F71" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G71" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I71" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>160</v>
       </c>
@@ -3117,8 +4611,17 @@
       <c r="F72" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G72" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="I72" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>162</v>
       </c>
@@ -3137,8 +4640,17 @@
       <c r="F73" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="G73" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="I73" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>164</v>
       </c>
@@ -3157,8 +4669,17 @@
       <c r="F74" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G74" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="I74" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>166</v>
       </c>
@@ -3177,8 +4698,17 @@
       <c r="F75" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G75" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="I75" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>168</v>
       </c>
@@ -3197,8 +4727,17 @@
       <c r="F76" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G76" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="I76" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>170</v>
       </c>
@@ -3217,8 +4756,17 @@
       <c r="F77" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G77" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="I77" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>172</v>
       </c>
@@ -3237,8 +4785,17 @@
       <c r="F78" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G78" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="I78" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>174</v>
       </c>
@@ -3257,8 +4814,17 @@
       <c r="F79" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G79" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="I79" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>175</v>
       </c>
@@ -3277,8 +4843,17 @@
       <c r="F80" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G80" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="I80" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>176</v>
       </c>
@@ -3297,8 +4872,17 @@
       <c r="F81" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G81" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I81" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>178</v>
       </c>
@@ -3317,8 +4901,17 @@
       <c r="F82" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G82" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="I82" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>180</v>
       </c>
@@ -3337,8 +4930,17 @@
       <c r="F83" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G83" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I83" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>181</v>
       </c>
@@ -3357,8 +4959,17 @@
       <c r="F84" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G84" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="I84" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>182</v>
       </c>
@@ -3377,8 +4988,17 @@
       <c r="F85" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G85" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="I85" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>183</v>
       </c>
@@ -3397,8 +5017,17 @@
       <c r="F86" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G86" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="I86" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>185</v>
       </c>
@@ -3417,8 +5046,17 @@
       <c r="F87" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G87" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="I87" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>187</v>
       </c>
@@ -3437,8 +5075,17 @@
       <c r="F88" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G88" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I88" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>189</v>
       </c>
@@ -3457,8 +5104,17 @@
       <c r="F89" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G89" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="I89" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>191</v>
       </c>
@@ -3477,8 +5133,17 @@
       <c r="F90" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G90" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="I90" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>193</v>
       </c>
@@ -3497,8 +5162,17 @@
       <c r="F91" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G91" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I91" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>195</v>
       </c>
@@ -3517,8 +5191,17 @@
       <c r="F92" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G92" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I92" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>198</v>
       </c>
@@ -3537,8 +5220,17 @@
       <c r="F93" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G93" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I93" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>200</v>
       </c>
@@ -3557,8 +5249,17 @@
       <c r="F94" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G94" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I94" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>202</v>
       </c>
@@ -3577,8 +5278,17 @@
       <c r="F95" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G95" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="I95" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>204</v>
       </c>
@@ -3597,8 +5307,17 @@
       <c r="F96" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G96" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="I96" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>206</v>
       </c>
@@ -3617,8 +5336,17 @@
       <c r="F97" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G97" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I97" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>209</v>
       </c>
@@ -3637,8 +5365,17 @@
       <c r="F98" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G98" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="I98" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>211</v>
       </c>
@@ -3657,8 +5394,17 @@
       <c r="F99" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G99" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="I99" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>213</v>
       </c>
@@ -3677,8 +5423,17 @@
       <c r="F100" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G100" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="I100" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>215</v>
       </c>
@@ -3697,8 +5452,17 @@
       <c r="F101" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G101" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I101" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>217</v>
       </c>
@@ -3717,8 +5481,17 @@
       <c r="F102" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G102" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="I102" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>219</v>
       </c>
@@ -3737,8 +5510,17 @@
       <c r="F103" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G103" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="I103" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>221</v>
       </c>
@@ -3757,8 +5539,17 @@
       <c r="F104" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G104" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="I104" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>223</v>
       </c>
@@ -3777,8 +5568,17 @@
       <c r="F105" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G105" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I105" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>226</v>
       </c>
@@ -3797,8 +5597,17 @@
       <c r="F106" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G106" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="I106" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>228</v>
       </c>
@@ -3817,8 +5626,17 @@
       <c r="F107" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G107" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="I107" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>231</v>
       </c>
@@ -3837,8 +5655,17 @@
       <c r="F108" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G108" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="I108" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>234</v>
       </c>
@@ -3857,8 +5684,17 @@
       <c r="F109" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G109" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="I109" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>237</v>
       </c>
@@ -3877,8 +5713,17 @@
       <c r="F110" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G110" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="I110" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>239</v>
       </c>
@@ -3897,8 +5742,17 @@
       <c r="F111" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G111" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="I111" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>241</v>
       </c>
@@ -3917,8 +5771,17 @@
       <c r="F112" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G112" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="I112" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>243</v>
       </c>
@@ -3937,8 +5800,17 @@
       <c r="F113" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G113" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="I113" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>246</v>
       </c>
@@ -3957,8 +5829,17 @@
       <c r="F114" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G114" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="I114" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>248</v>
       </c>
@@ -3977,8 +5858,17 @@
       <c r="F115" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G115" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="I115" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>251</v>
       </c>
@@ -3997,8 +5887,17 @@
       <c r="F116" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="G116" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="I116" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>253</v>
       </c>
@@ -4017,8 +5916,17 @@
       <c r="F117" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G117" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="I117" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>256</v>
       </c>
@@ -4037,8 +5945,17 @@
       <c r="F118" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G118" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="I118" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>258</v>
       </c>
@@ -4057,8 +5974,17 @@
       <c r="F119" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G119" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="I119" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>261</v>
       </c>
@@ -4077,8 +6003,17 @@
       <c r="F120" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G120" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="I120" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>263</v>
       </c>
@@ -4097,8 +6032,17 @@
       <c r="F121" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G121" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="I121" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>266</v>
       </c>
@@ -4117,8 +6061,17 @@
       <c r="F122" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G122" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="I122" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>268</v>
       </c>
@@ -4137,8 +6090,17 @@
       <c r="F123" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G123" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="I123" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>271</v>
       </c>
@@ -4157,8 +6119,17 @@
       <c r="F124" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G124" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="I124" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>273</v>
       </c>
@@ -4177,8 +6148,17 @@
       <c r="F125" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="G125" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="I125" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>276</v>
       </c>
@@ -4197,8 +6177,17 @@
       <c r="F126" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G126" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="I126" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>278</v>
       </c>
@@ -4217,8 +6206,17 @@
       <c r="F127" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G127" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>281</v>
       </c>
@@ -4237,8 +6235,17 @@
       <c r="F128" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G128" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="I128" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>284</v>
       </c>
@@ -4257,8 +6264,17 @@
       <c r="F129" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G129" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="I129" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>287</v>
       </c>
@@ -4277,8 +6293,17 @@
       <c r="F130" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G130" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="I130" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>289</v>
       </c>
@@ -4297,8 +6322,17 @@
       <c r="F131" s="1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G131" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="I131" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>291</v>
       </c>
@@ -4317,8 +6351,17 @@
       <c r="F132" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G132" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="I132" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>293</v>
       </c>
@@ -4337,8 +6380,17 @@
       <c r="F133" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G133" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="I133" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>295</v>
       </c>
@@ -4357,8 +6409,17 @@
       <c r="F134" s="1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G134" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="I134" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
@@ -4377,8 +6438,17 @@
       <c r="F135" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G135" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I135" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>299</v>
       </c>
@@ -4397,8 +6467,17 @@
       <c r="F136" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G136" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="I136" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>300</v>
       </c>
@@ -4417,8 +6496,17 @@
       <c r="F137" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G137" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="I137" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>301</v>
       </c>
@@ -4437,8 +6525,17 @@
       <c r="F138" s="1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G138" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="I138" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>304</v>
       </c>
@@ -4457,8 +6554,17 @@
       <c r="F139" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G139" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="I139" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>306</v>
       </c>
@@ -4477,8 +6583,17 @@
       <c r="F140" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G140" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="I140" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>308</v>
       </c>
@@ -4497,8 +6612,17 @@
       <c r="F141" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G141" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="I141" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>310</v>
       </c>
@@ -4517,8 +6641,17 @@
       <c r="F142" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G142" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I142" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>313</v>
       </c>
@@ -4537,8 +6670,17 @@
       <c r="F143" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G143" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="I143" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>315</v>
       </c>
@@ -4557,8 +6699,17 @@
       <c r="F144" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G144" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I144" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>317</v>
       </c>
@@ -4577,8 +6728,17 @@
       <c r="F145" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G145" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="I145" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>319</v>
       </c>
@@ -4597,8 +6757,17 @@
       <c r="F146" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G146" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="I146" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>322</v>
       </c>
@@ -4617,8 +6786,17 @@
       <c r="F147" s="1" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G147" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="I147" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>324</v>
       </c>
@@ -4637,8 +6815,17 @@
       <c r="F148" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G148" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="I148" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>327</v>
       </c>
@@ -4657,8 +6844,17 @@
       <c r="F149" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G149" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="I149" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>329</v>
       </c>
@@ -4677,8 +6873,17 @@
       <c r="F150" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G150" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="I150" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>332</v>
       </c>
@@ -4697,8 +6902,17 @@
       <c r="F151" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G151" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="I151" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>334</v>
       </c>
@@ -4717,8 +6931,17 @@
       <c r="F152" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G152" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>336</v>
       </c>
@@ -4737,8 +6960,17 @@
       <c r="F153" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G153" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="I153" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>338</v>
       </c>
@@ -4757,8 +6989,17 @@
       <c r="F154" s="1" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G154" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="I154" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>340</v>
       </c>
@@ -4777,8 +7018,17 @@
       <c r="F155" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G155" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="I155" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>342</v>
       </c>
@@ -4797,8 +7047,17 @@
       <c r="F156" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G156" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="I156" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>343</v>
       </c>
@@ -4817,8 +7076,17 @@
       <c r="F157" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G157" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="I157" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>345</v>
       </c>
@@ -4837,8 +7105,17 @@
       <c r="F158" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G158" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="I158" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>347</v>
       </c>
@@ -4857,8 +7134,17 @@
       <c r="F159" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G159" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="I159" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>350</v>
       </c>
@@ -4877,8 +7163,17 @@
       <c r="F160" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G160" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="I160" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>352</v>
       </c>
@@ -4896,6 +7191,15 @@
       </c>
       <c r="F161" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="I161" s="4">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
